--- a/network_specialist/past_prblems/past_problems.xlsx
+++ b/network_specialist/past_prblems/past_problems.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\security_specialist\network_tech\network_specialist\past_prblems\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B8ACE05-DDAB-4B49-9878-9DC984945B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ABFEACE-29D7-4000-9B92-E5F334E64C00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="330" yWindow="3345" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="まとめ" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t>回答日</t>
     <rPh sb="0" eb="3">
@@ -137,6 +137,10 @@
     <rPh sb="2" eb="4">
       <t>モンダイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>R3</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -477,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E2EC295-5F0F-4892-8D30-04652D76C42A}">
-  <dimension ref="B2:J6"/>
+  <dimension ref="B2:J7"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="2:10">
@@ -545,6 +549,17 @@
       </c>
       <c r="J6">
         <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10">
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/network_specialist/past_prblems/past_problems.xlsx
+++ b/network_specialist/past_prblems/past_problems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\security_specialist\network_tech\network_specialist\past_prblems\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ABFEACE-29D7-4000-9B92-E5F334E64C00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2202D11-A8A3-4032-B7A2-E44A7649742A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="330" yWindow="3345" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -561,6 +561,12 @@
       <c r="D7">
         <v>76</v>
       </c>
+      <c r="E7">
+        <v>40</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/network_specialist/past_prblems/past_problems.xlsx
+++ b/network_specialist/past_prblems/past_problems.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\security_specialist\network_tech\network_specialist\past_prblems\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2202D11-A8A3-4032-B7A2-E44A7649742A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ABC8BF1-E52B-41F0-8E9B-CA2E1F7A0D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="3345" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="まとめ" sheetId="2" r:id="rId1"/>
@@ -564,7 +564,19 @@
       <c r="E7">
         <v>40</v>
       </c>
+      <c r="F7">
+        <v>30</v>
+      </c>
+      <c r="G7">
+        <v>56</v>
+      </c>
       <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
         <v>1</v>
       </c>
     </row>

--- a/network_specialist/past_prblems/past_problems.xlsx
+++ b/network_specialist/past_prblems/past_problems.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\security_specialist\network_tech\network_specialist\past_prblems\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ABC8BF1-E52B-41F0-8E9B-CA2E1F7A0D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B81D2A5-9983-48BB-9DA8-AD34B2C67F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2685" yWindow="315" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="まとめ" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
   <si>
     <t>回答日</t>
     <rPh sb="0" eb="3">
@@ -141,6 +141,10 @@
   </si>
   <si>
     <t>R3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>R4</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -481,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E2EC295-5F0F-4892-8D30-04652D76C42A}">
-  <dimension ref="B2:J7"/>
+  <dimension ref="B2:J8"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="2:10">
@@ -578,6 +582,17 @@
       </c>
       <c r="J7">
         <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10">
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/network_specialist/past_prblems/past_problems.xlsx
+++ b/network_specialist/past_prblems/past_problems.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\security_specialist\network_tech\network_specialist\past_prblems\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B81D2A5-9983-48BB-9DA8-AD34B2C67F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D8250F0-FA27-4D7B-887D-35F80DFF7AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="315" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="まとめ" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
   <si>
     <t>回答日</t>
     <rPh sb="0" eb="3">
@@ -145,6 +145,10 @@
   </si>
   <si>
     <t>R4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>R5</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -485,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E2EC295-5F0F-4892-8D30-04652D76C42A}">
-  <dimension ref="B2:J8"/>
+  <dimension ref="B2:J9"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="2:10">
@@ -593,6 +597,35 @@
       </c>
       <c r="D8">
         <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10">
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9">
+        <v>72</v>
+      </c>
+      <c r="E9">
+        <v>36</v>
+      </c>
+      <c r="F9">
+        <v>24</v>
+      </c>
+      <c r="G9">
+        <v>58</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/network_specialist/past_prblems/past_problems.xlsx
+++ b/network_specialist/past_prblems/past_problems.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\security_specialist\network_tech\network_specialist\past_prblems\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D8250F0-FA27-4D7B-887D-35F80DFF7AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE4EB9C-FF3C-4E00-9ACE-CFC06C8E0969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="570" yWindow="1770" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="まとめ" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
   <si>
     <t>回答日</t>
     <rPh sb="0" eb="3">
@@ -149,6 +149,10 @@
   </si>
   <si>
     <t>R5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>R6</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -489,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E2EC295-5F0F-4892-8D30-04652D76C42A}">
-  <dimension ref="B2:J9"/>
+  <dimension ref="B2:J10"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="2:10">
@@ -625,6 +629,20 @@
         <v>2</v>
       </c>
       <c r="J9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10">
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10">
+        <v>38</v>
+      </c>
+      <c r="H10">
         <v>1</v>
       </c>
     </row>

--- a/network_specialist/past_prblems/past_problems.xlsx
+++ b/network_specialist/past_prblems/past_problems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\security_specialist\network_tech\network_specialist\past_prblems\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE4EB9C-FF3C-4E00-9ACE-CFC06C8E0969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{214CC336-48B9-42D7-8C13-7AE8925020D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="570" yWindow="1770" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -639,10 +639,25 @@
       <c r="C10" t="s">
         <v>14</v>
       </c>
+      <c r="D10">
+        <v>68</v>
+      </c>
       <c r="E10">
         <v>38</v>
       </c>
+      <c r="F10">
+        <v>36</v>
+      </c>
+      <c r="G10">
+        <v>63</v>
+      </c>
       <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>3</v>
+      </c>
+      <c r="J10">
         <v>1</v>
       </c>
     </row>

--- a/network_specialist/past_prblems/past_problems.xlsx
+++ b/network_specialist/past_prblems/past_problems.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\security_specialist\network_tech\network_specialist\past_prblems\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{214CC336-48B9-42D7-8C13-7AE8925020D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F34618-07AC-4879-9B29-AAE3011C4B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="570" yWindow="1770" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="まとめ" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
   <si>
     <t>回答日</t>
     <rPh sb="0" eb="3">
@@ -153,6 +153,10 @@
   </si>
   <si>
     <t>R6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Rwview</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -493,10 +497,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E2EC295-5F0F-4892-8D30-04652D76C42A}">
-  <dimension ref="B2:J10"/>
+  <dimension ref="B2:P10"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="2" spans="2:10">
+    <row r="2" spans="2:16">
       <c r="B2" t="s">
         <v>5</v>
       </c>
@@ -504,12 +508,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:16">
       <c r="H4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="2:10">
+      <c r="K4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16">
       <c r="B5" t="s">
         <v>9</v>
       </c>
@@ -533,8 +540,22 @@
       <c r="J5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="2:10">
+      <c r="K5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" s="3"/>
+      <c r="M5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="3"/>
+      <c r="P5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16">
       <c r="B6" t="s">
         <v>13</v>
       </c>
@@ -563,7 +584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:16">
       <c r="B7" t="s">
         <v>16</v>
       </c>
@@ -592,7 +613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:16">
       <c r="B8" t="s">
         <v>17</v>
       </c>
@@ -603,7 +624,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:16">
       <c r="B9" t="s">
         <v>18</v>
       </c>
@@ -631,8 +652,20 @@
       <c r="J9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="2:10">
+      <c r="K9">
+        <v>40</v>
+      </c>
+      <c r="M9">
+        <v>69</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16">
       <c r="B10" t="s">
         <v>19</v>
       </c>
@@ -662,9 +695,11 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="H5:I5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="N5:O5"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <hyperlinks>

--- a/network_specialist/past_prblems/past_problems.xlsx
+++ b/network_specialist/past_prblems/past_problems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\security_specialist\network_tech\network_specialist\past_prblems\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F34618-07AC-4879-9B29-AAE3011C4B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3793D93-EBB9-4E20-97C8-6A0FC2978434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -655,11 +655,17 @@
       <c r="K9">
         <v>40</v>
       </c>
+      <c r="L9">
+        <v>32</v>
+      </c>
       <c r="M9">
         <v>69</v>
       </c>
       <c r="N9">
         <v>1</v>
+      </c>
+      <c r="O9">
+        <v>2</v>
       </c>
       <c r="P9">
         <v>1</v>

--- a/network_specialist/past_prblems/past_problems.xlsx
+++ b/network_specialist/past_prblems/past_problems.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\security_specialist\network_tech\network_specialist\past_prblems\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3793D93-EBB9-4E20-97C8-6A0FC2978434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F3A2E76-4670-4725-AB4A-6380091ABD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2880" yWindow="1905" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="まとめ" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="23">
   <si>
     <t>回答日</t>
     <rPh sb="0" eb="3">
@@ -157,6 +157,17 @@
   </si>
   <si>
     <t>Rwview</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>H29</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>午前2</t>
+    <rPh sb="0" eb="2">
+      <t>ゴゼン</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -497,10 +508,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E2EC295-5F0F-4892-8D30-04652D76C42A}">
-  <dimension ref="B2:P10"/>
+  <dimension ref="B2:Q11"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="2" spans="2:16">
+    <row r="2" spans="2:17">
       <c r="B2" t="s">
         <v>5</v>
       </c>
@@ -508,7 +519,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="2:16">
+    <row r="4" spans="2:17">
       <c r="H4" t="s">
         <v>15</v>
       </c>
@@ -516,7 +527,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="2:16">
+    <row r="5" spans="2:17">
       <c r="B5" t="s">
         <v>9</v>
       </c>
@@ -554,8 +565,11 @@
       <c r="P5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="2:16">
+      <c r="Q5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17">
       <c r="B6" t="s">
         <v>13</v>
       </c>
@@ -584,7 +598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:16">
+    <row r="7" spans="2:17">
       <c r="B7" t="s">
         <v>16</v>
       </c>
@@ -613,7 +627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:16">
+    <row r="8" spans="2:17">
       <c r="B8" t="s">
         <v>17</v>
       </c>
@@ -624,7 +638,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="2:16">
+    <row r="9" spans="2:17">
       <c r="B9" t="s">
         <v>18</v>
       </c>
@@ -671,7 +685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="2:16">
+    <row r="10" spans="2:17">
       <c r="B10" t="s">
         <v>19</v>
       </c>
@@ -698,6 +712,26 @@
       </c>
       <c r="J10">
         <v>1</v>
+      </c>
+      <c r="L10">
+        <v>40</v>
+      </c>
+      <c r="O10">
+        <v>3</v>
+      </c>
+      <c r="Q10">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17">
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/network_specialist/past_prblems/past_problems.xlsx
+++ b/network_specialist/past_prblems/past_problems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\security_specialist\network_tech\network_specialist\past_prblems\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F3A2E76-4670-4725-AB4A-6380091ABD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF996393-BE30-426B-86E0-B974E95B4E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2880" yWindow="1905" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -716,8 +716,14 @@
       <c r="L10">
         <v>40</v>
       </c>
+      <c r="M10">
+        <v>74</v>
+      </c>
       <c r="O10">
         <v>3</v>
+      </c>
+      <c r="P10">
+        <v>2</v>
       </c>
       <c r="Q10">
         <v>76</v>

--- a/network_specialist/past_prblems/past_problems.xlsx
+++ b/network_specialist/past_prblems/past_problems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\security_specialist\network_tech\network_specialist\past_prblems\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF996393-BE30-426B-86E0-B974E95B4E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2707F346-242C-43B9-BC67-8D95C985E1F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2880" yWindow="1905" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
   <si>
     <t>回答日</t>
     <rPh sb="0" eb="3">
@@ -168,6 +168,10 @@
     <rPh sb="0" eb="2">
       <t>ゴゼン</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>R7</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -508,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E2EC295-5F0F-4892-8D30-04652D76C42A}">
-  <dimension ref="B2:Q11"/>
+  <dimension ref="B2:Q12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="2:17">
@@ -571,51 +575,33 @@
     </row>
     <row r="6" spans="2:17">
       <c r="B6" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
       </c>
       <c r="D6">
-        <v>64</v>
-      </c>
-      <c r="E6">
-        <v>40</v>
-      </c>
-      <c r="F6">
-        <v>40</v>
-      </c>
-      <c r="G6">
-        <v>65</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="2:17">
       <c r="B7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
       </c>
       <c r="D7">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="E7">
         <v>40</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G7">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -629,7 +615,7 @@
     </row>
     <row r="8" spans="2:17">
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
@@ -637,107 +623,136 @@
       <c r="D8">
         <v>76</v>
       </c>
+      <c r="E8">
+        <v>40</v>
+      </c>
+      <c r="F8">
+        <v>30</v>
+      </c>
+      <c r="G8">
+        <v>56</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:17">
       <c r="B9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
       </c>
       <c r="D9">
-        <v>72</v>
-      </c>
-      <c r="E9">
-        <v>36</v>
-      </c>
-      <c r="F9">
-        <v>24</v>
-      </c>
-      <c r="G9">
-        <v>58</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9">
-        <v>2</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9">
-        <v>40</v>
-      </c>
-      <c r="L9">
-        <v>32</v>
-      </c>
-      <c r="M9">
-        <v>69</v>
-      </c>
-      <c r="N9">
-        <v>1</v>
-      </c>
-      <c r="O9">
-        <v>2</v>
-      </c>
-      <c r="P9">
-        <v>1</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="2:17">
       <c r="B10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
       <c r="D10">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E10">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F10">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="G10">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
       <c r="I10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
+      <c r="K10">
+        <v>40</v>
+      </c>
       <c r="L10">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M10">
-        <v>74</v>
+        <v>69</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
       </c>
       <c r="O10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P10">
-        <v>2</v>
-      </c>
-      <c r="Q10">
-        <v>76</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="2:17">
       <c r="B11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
       </c>
       <c r="D11">
-        <v>80</v>
+        <v>68</v>
+      </c>
+      <c r="E11">
+        <v>38</v>
+      </c>
+      <c r="F11">
+        <v>36</v>
+      </c>
+      <c r="G11">
+        <v>63</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>3</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>40</v>
+      </c>
+      <c r="M11">
+        <v>74</v>
+      </c>
+      <c r="O11">
+        <v>3</v>
+      </c>
+      <c r="P11">
+        <v>2</v>
+      </c>
+      <c r="Q11">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17">
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/network_specialist/past_prblems/past_problems.xlsx
+++ b/network_specialist/past_prblems/past_problems.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\security_specialist\network_tech\network_specialist\past_prblems\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2707F346-242C-43B9-BC67-8D95C985E1F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C2372EB-7B2D-4590-81E3-F9C726EDBE35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2880" yWindow="1905" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="870" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="まとめ" sheetId="2" r:id="rId1"/>
@@ -652,6 +652,12 @@
       <c r="D9">
         <v>76</v>
       </c>
+      <c r="G9">
+        <v>64</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="2:17">
       <c r="B10" t="s">
@@ -728,11 +734,17 @@
       <c r="J11">
         <v>1</v>
       </c>
+      <c r="K11">
+        <v>36</v>
+      </c>
       <c r="L11">
         <v>40</v>
       </c>
       <c r="M11">
         <v>74</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
       </c>
       <c r="O11">
         <v>3</v>

--- a/network_specialist/past_prblems/past_problems.xlsx
+++ b/network_specialist/past_prblems/past_problems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\security_specialist\network_tech\network_specialist\past_prblems\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C2372EB-7B2D-4590-81E3-F9C726EDBE35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4CA3ED-6E0E-480E-BDFF-558307DEE4D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="870" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -652,8 +652,14 @@
       <c r="D9">
         <v>76</v>
       </c>
+      <c r="E9">
+        <v>34</v>
+      </c>
       <c r="G9">
         <v>64</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
       </c>
       <c r="J9">
         <v>1</v>

--- a/network_specialist/past_prblems/past_problems.xlsx
+++ b/network_specialist/past_prblems/past_problems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\security_specialist\network_tech\network_specialist\past_prblems\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4CA3ED-6E0E-480E-BDFF-558307DEE4D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B42D7CBD-1949-4D6E-92A0-AC37CFA861D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="870" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -655,14 +655,26 @@
       <c r="E9">
         <v>34</v>
       </c>
+      <c r="F9">
+        <v>40</v>
+      </c>
       <c r="G9">
         <v>64</v>
       </c>
       <c r="H9">
         <v>1</v>
       </c>
+      <c r="I9">
+        <v>3</v>
+      </c>
       <c r="J9">
         <v>1</v>
+      </c>
+      <c r="M9">
+        <v>78</v>
+      </c>
+      <c r="P9">
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="2:17">

--- a/network_specialist/past_prblems/past_problems.xlsx
+++ b/network_specialist/past_prblems/past_problems.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\security_specialist\network_tech\network_specialist\past_prblems\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B42D7CBD-1949-4D6E-92A0-AC37CFA861D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB7D646-6299-435A-BBC0-EE76927B42F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="870" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="まとめ" sheetId="2" r:id="rId1"/>
@@ -784,6 +784,24 @@
       <c r="D12">
         <v>72</v>
       </c>
+      <c r="E12">
+        <v>29</v>
+      </c>
+      <c r="F12">
+        <v>38</v>
+      </c>
+      <c r="G12">
+        <v>78</v>
+      </c>
+      <c r="H12">
+        <v>2</v>
+      </c>
+      <c r="I12">
+        <v>3</v>
+      </c>
+      <c r="J12">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
